--- a/episodes/data/blue_wave_squad.xlsx
+++ b/episodes/data/blue_wave_squad.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,16 +381,6 @@
           <t>club_country</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>league_tier</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -400,7 +390,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ArJany Martha</t>
+          <t>Armando Obispo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -410,22 +400,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>L</t>
+          <t>NLD</t>
         </is>
       </c>
     </row>
@@ -437,7 +417,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Armando Obispo</t>
+          <t>Deveron Fonville</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -447,22 +427,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>NLD</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>H</t>
         </is>
       </c>
     </row>
@@ -474,7 +444,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cuco Martina</t>
+          <t>Joshua Brenet</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -484,22 +454,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>L</t>
+          <t>TUR</t>
         </is>
       </c>
     </row>
@@ -511,7 +471,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Deveron Fonville</t>
+          <t>Juriën Gaari</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -521,22 +481,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NEC Nijmegen</t>
+          <t>Abha</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>NLD</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>SAU</t>
         </is>
       </c>
     </row>
@@ -548,7 +498,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Joshua Brenet</t>
+          <t>Riechedly Bazoer</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -558,22 +508,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>TUR</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>H</t>
         </is>
       </c>
     </row>
@@ -585,7 +525,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Juriën Gaari</t>
+          <t>Roshon van Eijma</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -595,22 +535,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Abha</t>
+          <t>A.E. Kifisia</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SAU</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>GRC</t>
         </is>
       </c>
     </row>
@@ -622,7 +552,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Riechedly Bazoer</t>
+          <t>Sherel Floranus</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -632,22 +562,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>TUR</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>NLD</t>
         </is>
       </c>
     </row>
@@ -659,7 +579,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Roshon van Eijma</t>
+          <t>Shurandy Sambo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -669,22 +589,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>NLD</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>H</t>
         </is>
       </c>
     </row>
@@ -696,32 +606,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sherel Floranus</t>
+          <t>Brandley Kuwas</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>NLD</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>H</t>
         </is>
       </c>
     </row>
@@ -733,32 +633,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Shurandy Sambo</t>
+          <t>Gervane Kastaneer</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>NLD</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>MYS</t>
         </is>
       </c>
     </row>
@@ -770,32 +660,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tyrique Mercera</t>
+          <t>Jearl Margaritha</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Beveren</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>L</t>
+          <t>BEL</t>
         </is>
       </c>
     </row>
@@ -807,7 +687,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Gervane Kastaneer</t>
+          <t>Jeremy Antonisse</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -817,22 +697,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>A.E. Kifisia</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MYS</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>GRC</t>
         </is>
       </c>
     </row>
@@ -844,7 +714,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Jeremy Antonisse</t>
+          <t>Jürgen Locadia</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -854,22 +724,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Miami FC</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>GRC</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
@@ -881,7 +741,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Joshua Zimmerman</t>
+          <t>Kenji Gorré</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -891,22 +751,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>L</t>
+          <t>ISR</t>
         </is>
       </c>
     </row>
@@ -918,7 +768,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jürgen Locadia</t>
+          <t>Sontje Hansen</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -928,22 +778,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Miami FC</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>GBR</t>
         </is>
       </c>
     </row>
@@ -955,7 +795,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rangelo Janga</t>
+          <t>Tahith Chong</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -965,22 +805,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>unknown/free agent</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>L</t>
+          <t>GBR</t>
         </is>
       </c>
     </row>
@@ -992,32 +822,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sontje Hansen</t>
+          <t>Eloy Room</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FWD</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Miami FC</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>GBR</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
@@ -1029,7 +849,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Eloy Room</t>
+          <t>Trevor Doornbusch</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1039,22 +859,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Miami FC</t>
+          <t>VVV-Venlo</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>NLD</t>
         </is>
       </c>
     </row>
@@ -1066,7 +876,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Trevor Doornbusch</t>
+          <t>Tyrick Bodak</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1076,22 +886,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VVV-Venlo</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>NLD</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>H</t>
         </is>
       </c>
     </row>
@@ -1103,32 +903,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tyrick Bodak</t>
+          <t>Ar'jany Martha</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GK</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>NLD</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>GBR</t>
         </is>
       </c>
     </row>
@@ -1140,7 +930,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Brandley Kuwas</t>
+          <t>Godfried Roemeratoe</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1150,22 +940,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>L</t>
+          <t>NLD</t>
         </is>
       </c>
     </row>
@@ -1177,7 +957,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Godfried Roemeratoe</t>
+          <t>Juninho Bacuna</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1187,22 +967,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>NLD</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>H</t>
         </is>
       </c>
     </row>
@@ -1214,7 +984,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Jearl Margaritha</t>
+          <t>Kevin Felida</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1224,22 +994,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>L</t>
+          <t>NLD</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1011,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Jordi Paulina</t>
+          <t>Leandro Bacuna (captain)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1261,22 +1021,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Iğdır</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>DEU</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>TUR</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1038,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Juninho Bacuna</t>
+          <t>Livano Comenencia</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1298,22 +1048,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>FC Volendam</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>NLD</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>CHE</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1065,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Kenji Gorré</t>
+          <t>Tyrese Noslin</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1335,244 +1075,174 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>L</t>
+          <t>GBR</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CUW-M</t>
+          <t>CUW-W</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kevin Felida</t>
+          <t>Charnainelys Andrea</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>FC Den Bosch</t>
+          <t>Excellence</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>NLD</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>CUW</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CUW-M</t>
+          <t>CUW-W</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Leandro Bacuna</t>
+          <t>Diangely's Strijdhaftig</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Iğdır FK</t>
+          <t>FC Skillz</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>TUR</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>NLD</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CUW-M</t>
+          <t>CUW-W</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Livano Comenencia</t>
+          <t>Ignarda Pieternella</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>FC Zürich</t>
+          <t>Victory Boys</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CHE</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>CUW</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CUW-M</t>
+          <t>CUW-W</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Rayvien Rosario</t>
+          <t>Ludmarie Flaneur</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>BVV Barendrecht</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>L</t>
+          <t>NLD</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CUW-M</t>
+          <t>CUW-W</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tahith Chong</t>
+          <t>Naychelene Nisia</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>GBR</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>NLD</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CUW-M</t>
+          <t>CUW-W</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tyrese Noslin</t>
+          <t>Rozan Snoek</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>RKSV HBC</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>NLD</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>H</t>
         </is>
       </c>
     </row>
@@ -1584,32 +1254,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Akisha Lohman</t>
+          <t>Ruwenna Cristina</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Be Quick '28</t>
+          <t>UNDEBA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>NLD</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>CUW</t>
         </is>
       </c>
     </row>
@@ -1621,32 +1281,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Charnainelys Andrea</t>
+          <t>Chelsea Kenton</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Excellence</t>
+          <t>WV-HEDW</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CUW</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>NLD</t>
         </is>
       </c>
     </row>
@@ -1658,32 +1308,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Chelsea Kenton</t>
+          <t>Destiny Koko</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>WHC Hedw</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>NLD</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>H</t>
         </is>
       </c>
     </row>
@@ -1695,32 +1335,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Destiny Koko</t>
+          <t>Gervionna Martina</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Victory Boys</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>NLD</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>CUW</t>
         </is>
       </c>
     </row>
@@ -1732,32 +1362,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Diangely's Strijdhaftig</t>
+          <t>Kadisha Martina (captain)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>FC Skillz</t>
+          <t>Cumberland Phoenix</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>CUW</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
@@ -1769,32 +1389,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Gervionna Martina</t>
+          <t>Raëngelly Keller</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Victory Boys</t>
+          <t>Be Quick '28</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CUW</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>NLD</t>
         </is>
       </c>
     </row>
@@ -1806,32 +1416,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ignarda Pieternella</t>
+          <t>Shi-jona Martina</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Victory Boys</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>CUW</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>NLD</t>
         </is>
       </c>
     </row>
@@ -1843,32 +1443,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Jeleaugh Rosa</t>
+          <t>Taïsha Hansen</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Acharnaikos</t>
+          <t>Be Quick '28</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>GRC</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>NLD</t>
         </is>
       </c>
     </row>
@@ -1880,32 +1470,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Kadisha Martina</t>
+          <t>Kingnaichely Provence</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Cumberland University</t>
+          <t>Jong Holland</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>CUW</t>
         </is>
       </c>
     </row>
@@ -1917,32 +1497,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Kingnaichely Provence</t>
+          <t>Thiheyna Susana</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Jong Holland</t>
+          <t>Undeba</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>CUW</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>H</t>
         </is>
       </c>
     </row>
@@ -1954,32 +1524,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Kyara Bernadina</t>
+          <t>Akisha Lohman</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>FC Skillz</t>
+          <t>Be Quick '28</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>CUW</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>NLD</t>
         </is>
       </c>
     </row>
@@ -1991,32 +1551,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Lindsey Hart</t>
+          <t>Jeleaugh Rosa</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Excelsior Maassluis</t>
+          <t>Acharnaikos Women Football Club</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>NLD</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>GRC</t>
         </is>
       </c>
     </row>
@@ -2028,32 +1578,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ludmarie Flaneur</t>
+          <t>Kyara Bernadina</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>BVV Barendrecht</t>
+          <t>FC Skillz [nl]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>NLD</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>H</t>
         </is>
       </c>
     </row>
@@ -2065,32 +1605,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Naychelene Nisia</t>
+          <t>Lindsey Hart</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Excelsior Maassluis</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>NLD</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>H</t>
         </is>
       </c>
     </row>
@@ -2102,32 +1632,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Raëngelly Keller</t>
+          <t>Riesmarly Tokaay</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Be Quick '28</t>
+          <t>Victory Boys</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>NLD</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>CUW</t>
         </is>
       </c>
     </row>
@@ -2139,254 +1659,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Riesmarly Tokaay</t>
+          <t>Shermilyene Leito</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Victory Boys</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CUW</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>CUW-W</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Rozan Snoek</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>HBC</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>NLD</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>CUW-W</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Ruwenna Cristina</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>UNDEBA</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>CUW</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>CUW-W</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Shermilyene Leito</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>MSV Duisburg</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
           <t>DEU</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>CUW-W</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Shi-Jona Martina</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>NLD</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>CUW-W</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Taïsha Hansen</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Be Quick '28</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>NLD</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>CUW-W</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Thiheyna Susana</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Excellence</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>CUW</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>H</t>
         </is>
       </c>
     </row>
@@ -2397,7 +1685,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2426,16 +1714,6 @@
           <t>club_country</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>league_tier</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2463,16 +1741,6 @@
           <t>NLD</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2492,22 +1760,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>OFC Oostzaan</t>
+          <t>Lisse</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>NLD</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>H</t>
         </is>
       </c>
     </row>
@@ -2529,22 +1787,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Jong Sparta Rotterdam</t>
+          <t>Dakota</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>NLD</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>ABW</t>
         </is>
       </c>
     </row>
@@ -2566,22 +1814,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Aruba (local club)</t>
+          <t>FC Prishtina</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ABW</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>XKX</t>
         </is>
       </c>
     </row>
@@ -2593,7 +1831,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Jeremy Trimon</t>
+          <t>Kymani Nedd</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2603,22 +1841,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Aruba (local club)</t>
+          <t>VV Zwaluwen</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ABW</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>NLD</t>
         </is>
       </c>
     </row>
@@ -2630,7 +1858,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kymani Nedd</t>
+          <t>Nickenson Paul</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2640,22 +1868,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Aruba (local club)</t>
+          <t>Dakota</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>ABW</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>H</t>
         </is>
       </c>
     </row>
@@ -2667,7 +1885,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nickenson Paul</t>
+          <t>Rainey Breinburg</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2677,22 +1895,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Aruba (local club)</t>
+          <t>Excelsior U21</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ABW</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>NLD</t>
         </is>
       </c>
     </row>
@@ -2704,7 +1912,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rainey Breinburg</t>
+          <t>Rovien Ostiana</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2714,22 +1922,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Feyenoord U19</t>
+          <t>TOGB</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>NLD</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>H</t>
         </is>
       </c>
     </row>
@@ -2741,7 +1939,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Carlito Fermina</t>
+          <t>Arenchelo Leito</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2751,22 +1949,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Kozakken Boys</t>
+          <t>RKAV Volendam</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>NLD</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>H</t>
         </is>
       </c>
     </row>
@@ -2778,7 +1966,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Conner van Kilsdonk</t>
+          <t>Carlito Fermina</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2788,22 +1976,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>TOP Oss</t>
+          <t>Kozakken Boys</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>NLD</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>H</t>
         </is>
       </c>
     </row>
@@ -2833,16 +2011,6 @@
           <t>NLD</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2862,22 +2030,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Aruba (local club)</t>
+          <t>Schwarz-Weiß Rehden</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ABW</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>DEU</t>
         </is>
       </c>
     </row>
@@ -2899,22 +2057,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Aruba (local club)</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ABW</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>NLD</t>
         </is>
       </c>
     </row>
@@ -2926,32 +2074,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Jahmani Eisden</t>
+          <t>Mishawn Molina</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GK</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Aruba (local club)</t>
+          <t>Willem II U21</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ABW</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>NLD</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2101,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Josthan Maduro</t>
+          <t>Jahmani Eisden</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2973,22 +2111,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Aruba (local club)</t>
+          <t>Sportlust '46</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ABW</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>NLD</t>
         </is>
       </c>
     </row>
@@ -3000,7 +2128,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Matthew Lentink</t>
+          <t>Josthan Maduro</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3010,22 +2138,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Roosendaal</t>
+          <t>SV Britannia</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>NLD</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>ABW</t>
         </is>
       </c>
     </row>
@@ -3037,7 +2155,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Shafeeq Toussaint</t>
+          <t>Matthew Lentink</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -3047,22 +2165,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FC Den Bosch</t>
+          <t>Goes</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>NLD</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>H</t>
         </is>
       </c>
     </row>
@@ -3074,7 +2182,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Arenchelo Leito</t>
+          <t>Conner van Kilsdonk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -3084,22 +2192,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>RKAV Volendam</t>
+          <t>TOP Oss</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>NLD</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>H</t>
         </is>
       </c>
     </row>
@@ -3121,22 +2219,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Aruba (local club)</t>
+          <t>AFC '34</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ABW</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>NLD</t>
         </is>
       </c>
     </row>
@@ -3158,22 +2246,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Aruba (local club)</t>
+          <t>Kloetinge</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ABW</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>NLD</t>
         </is>
       </c>
     </row>
@@ -3185,7 +2263,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Jaybriën Romano</t>
+          <t>Jaybrien Romano</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3195,22 +2273,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Aruba (local club)</t>
+          <t>Halsteren</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ABW</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>NLD</t>
         </is>
       </c>
     </row>
@@ -3222,7 +2290,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Jayden Ngadiman</t>
+          <t>Quinlan Poulina</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3232,22 +2300,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Aruba (local club)</t>
+          <t>Lisse</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ABW</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>NLD</t>
         </is>
       </c>
     </row>
@@ -3259,7 +2317,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mishawn Molina</t>
+          <t>Walter Bennett</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3269,133 +2327,93 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Aruba (local club)</t>
+          <t>SC Feyenoord</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ABW</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>NLD</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ARU-M</t>
+          <t>ARU-W</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Quinlan Poulina</t>
+          <t>Dyviënne Henriquez</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Katwijk</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>NLD</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>X</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ARU-M</t>
+          <t>ARU-W</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Roviën Ostiana</t>
+          <t>Genesis Hazel</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Jong FC Volendam</t>
+          <t>Excelsior Rotterdam</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>NLD</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>H</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ARU-M</t>
+          <t>ARU-W</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Walter Bennett</t>
+          <t>Jayla Croes</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Aruba (local club)</t>
+          <t>FC Skillz</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ABW</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>NLD</t>
         </is>
       </c>
     </row>
@@ -3407,7 +2425,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Dyviënne Henriquez</t>
+          <t>Joya Tromp</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3423,16 +2441,6 @@
       <c r="E28" t="inlineStr">
         <is>
           <t>X</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>U</t>
         </is>
       </c>
     </row>
@@ -3444,7 +2452,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Genesis Hazel</t>
+          <t>Joyce Chen</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3454,22 +2462,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam (youth)</t>
+          <t>SV Racing Club</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>NLD</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>M</t>
+          <t>ABW</t>
         </is>
       </c>
     </row>
@@ -3481,7 +2479,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Jayla Croes</t>
+          <t>Michaela Netto</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3491,22 +2489,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>FC Skillz</t>
+          <t>FC Utrecht</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>NLD</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>H</t>
         </is>
       </c>
     </row>
@@ -3518,7 +2506,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Joya Tromp</t>
+          <t>Sofia Mora</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3528,22 +2516,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SV Deportivo Nacional</t>
+          <t>SV Bubali</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>ABW</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>M</t>
         </is>
       </c>
     </row>
@@ -3555,32 +2533,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Joyce Chen</t>
+          <t>Bonny Lammers</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>SV Racing Club Aruba</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ABW</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>NLD</t>
         </is>
       </c>
     </row>
@@ -3592,32 +2560,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Michaela Netto</t>
+          <t>Jill Dreischor</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Jong FC Utrecht</t>
+          <t>VV Nieuwenhoorn</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>NLD</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>M</t>
         </is>
       </c>
     </row>
@@ -3629,32 +2587,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sofia Mora</t>
+          <t>Vanessa Susanna</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SV Bubali</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ABW</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>NLD</t>
         </is>
       </c>
     </row>
@@ -3666,7 +2614,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bonny Lammers Solognier</t>
+          <t>Zyana Rogers</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3676,22 +2624,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>SV Britannia</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>NLD</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>ABW</t>
         </is>
       </c>
     </row>
@@ -3703,32 +2641,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Jill Dreischor</t>
+          <t>Dylana Veenstra</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>FWD</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VV Nieuwenhoorn</t>
+          <t>SV Britannia</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>NLD</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>M</t>
+          <t>ABW</t>
         </is>
       </c>
     </row>
@@ -3740,32 +2668,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Vanessa Susanna</t>
+          <t>Hadassah Kock</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>FWD</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>NLD</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>H</t>
         </is>
       </c>
     </row>
@@ -3777,32 +2695,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Zyana Rogers</t>
+          <t>Richdienne Croes</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FWD</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SV Britannia</t>
+          <t>Forum Sport</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ABW</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>M</t>
+          <t>NLD</t>
         </is>
       </c>
     </row>
@@ -3814,32 +2722,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Dylana Veenstra</t>
+          <t>Adannayah Breinburg</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>GK</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SV Britannia</t>
+          <t>Excelsior Rotterdam</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ABW</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>NLD</t>
         </is>
       </c>
     </row>
@@ -3851,32 +2749,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Hadassah Kock</t>
+          <t>Aisse Gumbs</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GK</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>NLD</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>M</t>
+          <t>GRC</t>
         </is>
       </c>
     </row>
@@ -3888,32 +2776,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Richdienne Croes</t>
+          <t>Delilah Croes</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GK</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Forum Sport</t>
+          <t>FC Skillz</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>NLD</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>M</t>
         </is>
       </c>
     </row>
@@ -3925,7 +2803,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Adannayah Breinburg</t>
+          <t>Izaline Angela</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3935,22 +2813,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam (MO17 youth)</t>
+          <t>FC Rijnvogels</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>NLD</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>H</t>
         </is>
       </c>
     </row>
@@ -3962,7 +2830,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Aisse Gumbs</t>
+          <t>Jennifer Henao</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3972,22 +2840,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>AA Gent</t>
+          <t>SV Britannia</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>BEL</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>ABW</t>
         </is>
       </c>
     </row>
@@ -3999,7 +2857,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Delilah Croes</t>
+          <t>Kim Schoppema</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4009,22 +2867,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>FC Skillz</t>
+          <t>SV Britannia</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>NLD</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>ABW</t>
         </is>
       </c>
     </row>
@@ -4036,7 +2884,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Izaline Angela</t>
+          <t>Niamh Tromp</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4046,22 +2894,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>FC Rijnvogels</t>
+          <t>NEC Nijmegen</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>NLD</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>H</t>
         </is>
       </c>
     </row>
@@ -4073,7 +2911,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Jennifer Henao Garces</t>
+          <t>Soraya Verhoeve(Captain)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4083,22 +2921,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>SV Britannia</t>
+          <t>FC Utrecht</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ABW</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>NLD</t>
         </is>
       </c>
     </row>
@@ -4110,7 +2938,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Kim Schoppema</t>
+          <t>Tarianna Doornkamp</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4120,133 +2948,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>SV Britannia</t>
+          <t>FC Rijnvogels</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ABW</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>ARU-W</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Niamh Tromp</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>NEC Nijmegen (youth)</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>NLD</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>ARU-W</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Soraya Verhoeve</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>FC Utrecht</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>NLD</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>ARU-W</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Tarianna Doornkamp</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>FC Rijnvogels</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>NLD</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>NLD</t>
         </is>
       </c>
     </row>
